--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1977831</v>
+        <v>120553329</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodbergsplatån, Jmt</t>
+          <t>Bodbergsplatåns sydöstra del, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520418.9306968668</v>
+        <v>520215</v>
       </c>
       <c r="R2" t="n">
-        <v>6953030.629411181</v>
+        <v>6952795</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,26 +757,254 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
+        </is>
+      </c>
       <c r="AN2" t="n">
         <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120553330</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bodbergsplatåns sydöstra del, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>520220</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6952779</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>hänglavsrik 140-årig barrnaturskog i östsida</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga med mossa på</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1977831</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodbergsplatån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520419</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6953031</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2011-09-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2011-09-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,107 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135534930</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520328</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6953087</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120553330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1977831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534930</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>135534930</v>
       </c>
       <c r="B5" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>135534930</v>
       </c>
       <c r="B5" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,112 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1977831</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135534930</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520328</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6953087</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135534930</t>
         </is>
       </c>
     </row>
@@ -1035,6 +1141,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>135534930</v>
       </c>
       <c r="B5" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41486-2024 artfynd.xlsx
+++ b/artfynd/A 41486-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>135534930</v>
       </c>
       <c r="B5" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
